--- a/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
+++ b/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">A relation that holds between an interventions mechanism of action and an entity x, in which the entity x  participates in or is part of the mechanism of action process and is influenced by a BCI or its context such that there is some change in entity x. </t>
+          <t>A relation that holds between an behaviour change intervention mechanism of action and an entity (x), if (1) x participates in or is part of the mechanism of action process and (2) x is influenced by the behavior change intervention in some scenario such that there is some change in entity x.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">

--- a/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
+++ b/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1426,22 +1426,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BFO:0000054</t>
+          <t>AFO:0000062</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>realised in</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>realized in [BFO:0000054]</t>
+          <t>preceded by</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>temporally related to [RO:0002222]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Inverse of realizes relation.</t>
+          <t>x is preceded by y if and only if the time point at which y ends is before or equivalent to the time point at which x starts. Formally: x preceded by y iff ω(y) &lt;= α(x), where α is a function that maps a process to a start point, and ω is a function that maps a process to an end point.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1454,83 +1455,150 @@
           <t>occurrent</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BFO:0000055</t>
+          <t>AFO:0000063</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>realises</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>realizes [BFO:0000055]</t>
+          <t>precedes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>temporally related to [RO:0002222]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>To say that b realizes c at t is to assert that there is some material entity d and b is a process which has participant d at t and c is a disposition or role of which d is bearer_of at tand the type instantiated by b is correlated with the type instantiated by c.</t>
-        </is>
-      </c>
+          <t>x precedes y if and only if the time point at which x ends is before or equivalent to the time point at which y starts. Formally: x precedes y iff ω(x) &lt;= α(y), where α is a function that maps a process to a start point, and ω is a function that maps a process to an end point.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIOR:000008</t>
+          <t>BFO:0000054</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>through</t>
+          <t>realised in</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>realized in [BFO:0000054]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>A relation that holds between an behaviour change intervention mechanism of action and an entity (x), if (1) x participates in or is part of the mechanism of action process and (2) x is influenced by the behavior change intervention in some scenario such that there is some change in entity x.</t>
+          <t>Inverse of realizes relation.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>behaviour change intervention mechanism of action</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>entity [BFO:0000001]</t>
+          <t>occurrent</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>BFO:0000055</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>realises</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>realizes [BFO:0000055]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>To say that b realizes c at t is to assert that there is some material entity d and b is a process which has participant d at t and c is a disposition or role of which d is bearer_of at tand the type instantiated by b is correlated with the type instantiated by c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BCIOR:000008</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>through</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>A relation that holds between an behaviour change intervention mechanism of action and an entity (x), if (1) x participates in or is part of the mechanism of action process and (2) x is influenced by the behavior change intervention in some scenario such that there is some change in entity x.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>behaviour change intervention mechanism of action</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>BCIOR:000015</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>uses</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>has participant [RO:0000057]</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Has participant that relates a behaviour to a material entity that the person enacting the behaviour intends to enable or facilitate the behaviour.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>individual human behaviour</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>

--- a/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
+++ b/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
@@ -1426,7 +1426,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AFO:0000062</t>
+          <t>BFO:0000062</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1434,7 +1434,6 @@
           <t>preceded by</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>temporally related to [RO:0002222]</t>
@@ -1455,12 +1454,11 @@
           <t>occurrent</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AFO:0000063</t>
+          <t>BFO:0000063</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1468,7 +1466,6 @@
           <t>precedes</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>temporally related to [RO:0002222]</t>
@@ -1489,7 +1486,6 @@
           <t>occurrent</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">

--- a/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
+++ b/Upper Level BCIO/inputs/BCIO_Upper_Rels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe-my.sharepoint.com/personal/maya_braun_ugent_be/Documents/Documenten/GitHub/ontologies/Upper Level BCIO/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_1C75A39D551ADEA65576CB524C5ED87656CD452E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{131E8564-06D1-4C87-918F-25532A3667A9}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="11_1C75A39D551ADEA65576CB524C5ED87656CD452E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59C6D843-EE90-42B7-96D4-6C7FA3C599E1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -541,9 +541,6 @@
     <t>material entity</t>
   </si>
   <si>
-    <t>Curation</t>
-  </si>
-  <si>
     <t>External</t>
   </si>
   <si>
@@ -551,6 +548,9 @@
   </si>
   <si>
     <t>Obsolete</t>
+  </si>
+  <si>
+    <t>Curation status</t>
   </si>
 </sst>
 </file>
@@ -609,6 +609,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -928,7 +932,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -948,7 +952,7 @@
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -968,7 +972,7 @@
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -991,7 +995,7 @@
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -1014,7 +1018,7 @@
         <v>26</v>
       </c>
       <c r="I5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -1037,7 +1041,7 @@
         <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -1060,7 +1064,7 @@
         <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -1083,7 +1087,7 @@
         <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -1106,7 +1110,7 @@
         <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1123,7 +1127,7 @@
         <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1146,7 +1150,7 @@
         <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1169,7 +1173,7 @@
         <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1192,7 +1196,7 @@
         <v>11</v>
       </c>
       <c r="I13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1215,7 +1219,7 @@
         <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1235,7 +1239,7 @@
         <v>70</v>
       </c>
       <c r="I15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1252,7 +1256,7 @@
         <v>74</v>
       </c>
       <c r="I16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1275,7 +1279,7 @@
         <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1292,7 +1296,7 @@
         <v>81</v>
       </c>
       <c r="I18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1309,7 +1313,7 @@
         <v>85</v>
       </c>
       <c r="I19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1326,7 +1330,7 @@
         <v>89</v>
       </c>
       <c r="I20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1343,7 +1347,7 @@
         <v>93</v>
       </c>
       <c r="I21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1360,7 +1364,7 @@
         <v>97</v>
       </c>
       <c r="I22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1383,7 +1387,7 @@
         <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1406,7 +1410,7 @@
         <v>104</v>
       </c>
       <c r="I24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1429,7 +1433,7 @@
         <v>108</v>
       </c>
       <c r="I25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1446,7 +1450,7 @@
         <v>111</v>
       </c>
       <c r="I26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1463,7 +1467,7 @@
         <v>115</v>
       </c>
       <c r="I27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1480,7 +1484,7 @@
         <v>61</v>
       </c>
       <c r="I28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1503,7 +1507,7 @@
         <v>66</v>
       </c>
       <c r="I29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1520,7 +1524,7 @@
         <v>125</v>
       </c>
       <c r="I30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1537,7 +1541,7 @@
         <v>129</v>
       </c>
       <c r="I31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1560,7 +1564,7 @@
         <v>34</v>
       </c>
       <c r="I32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1580,7 +1584,7 @@
         <v>137</v>
       </c>
       <c r="I33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1597,7 +1601,7 @@
         <v>141</v>
       </c>
       <c r="I34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1620,7 +1624,7 @@
         <v>11</v>
       </c>
       <c r="I35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1637,7 +1641,7 @@
         <v>149</v>
       </c>
       <c r="I36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1660,7 +1664,7 @@
         <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1683,7 +1687,7 @@
         <v>34</v>
       </c>
       <c r="I38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1706,7 +1710,7 @@
         <v>34</v>
       </c>
       <c r="I39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1723,7 +1727,7 @@
         <v>163</v>
       </c>
       <c r="I40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1743,7 +1747,7 @@
         <v>168</v>
       </c>
       <c r="I41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1766,7 +1770,7 @@
         <v>172</v>
       </c>
       <c r="I42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
